--- a/tables/Pop_Sizes.xlsx
+++ b/tables/Pop_Sizes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_RWD\Bison_github\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6190216F-8BDC-4DB8-8CD7-6B8A979A9690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0ADDC20-9953-4F5E-AE86-D5035243767F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-118" yWindow="-118" windowWidth="20343" windowHeight="12934" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -562,16 +562,34 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -581,24 +599,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -882,24 +882,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X31"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="25.33203125" style="2" customWidth="1"/>
-    <col min="3" max="4" width="23.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="22.33203125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="47.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.5546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="23" style="2" customWidth="1"/>
-    <col min="11" max="11" width="52.33203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" style="2" customWidth="1"/>
+    <col min="3" max="4" width="23.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="47.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="40.85546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="26.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="52.28515625" style="2" customWidth="1"/>
     <col min="12" max="12" width="27" style="2" customWidth="1"/>
-    <col min="13" max="24" width="9.109375" style="2"/>
-    <col min="25" max="16384" width="9.109375" style="3"/>
+    <col min="13" max="24" width="9.140625" style="2"/>
+    <col min="25" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17.05" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="17.100000000000001" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>19</v>
       </c>
@@ -938,20 +938,20 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23" t="s">
+      <c r="C2" s="29"/>
+      <c r="D2" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="24">
         <v>11000</v>
       </c>
       <c r="G2" s="13" t="s">
@@ -963,23 +963,23 @@
       <c r="I2" s="8">
         <v>34</v>
       </c>
-      <c r="J2" s="26" t="s">
+      <c r="J2" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="L2" s="26" t="s">
+      <c r="L2" s="20" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
       <c r="G3" s="13" t="s">
         <v>59</v>
       </c>
@@ -989,17 +989,17 @@
       <c r="I3" s="6">
         <v>10</v>
       </c>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="26"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
       <c r="G4" s="13" t="s">
         <v>28</v>
       </c>
@@ -1009,17 +1009,17 @@
       <c r="I4" s="8">
         <v>50</v>
       </c>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="26"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
       <c r="G5" s="14" t="s">
         <v>29</v>
       </c>
@@ -1029,23 +1029,23 @@
       <c r="I5" s="6">
         <v>48</v>
       </c>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="26"/>
-      <c r="B6" s="19" t="s">
+      <c r="A6" s="20"/>
+      <c r="B6" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19" t="s">
+      <c r="C6" s="22"/>
+      <c r="D6" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="27">
         <v>3800</v>
       </c>
       <c r="G6" s="15" t="s">
@@ -1057,21 +1057,21 @@
       <c r="I6" s="9">
         <v>13</v>
       </c>
-      <c r="J6" s="19" t="s">
+      <c r="J6" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="K6" s="19" t="s">
+      <c r="K6" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="L6" s="19"/>
+      <c r="L6" s="22"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="26"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
       <c r="G7" s="16" t="s">
         <v>32</v>
       </c>
@@ -1081,23 +1081,23 @@
       <c r="I7" s="7">
         <v>9</v>
       </c>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="26"/>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="20"/>
+      <c r="B8" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21" t="s">
+      <c r="C8" s="19"/>
+      <c r="D8" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="19">
         <v>58</v>
       </c>
       <c r="G8" s="13" t="s">
@@ -1109,19 +1109,19 @@
       <c r="I8" s="8">
         <v>11</v>
       </c>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21" t="s">
+      <c r="J8" s="19"/>
+      <c r="K8" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="L8" s="21"/>
+      <c r="L8" s="19"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="26"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
       <c r="G9" s="14" t="s">
         <v>58</v>
       </c>
@@ -1131,12 +1131,12 @@
       <c r="I9" s="6">
         <v>2</v>
       </c>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
+      <c r="A10" s="20"/>
       <c r="B10" s="9" t="s">
         <v>38</v>
       </c>
@@ -1170,7 +1170,7 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="26"/>
+      <c r="A11" s="20"/>
       <c r="B11" s="8" t="s">
         <v>7</v>
       </c>
@@ -1204,7 +1204,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="26"/>
+      <c r="A12" s="20"/>
       <c r="B12" s="9" t="s">
         <v>41</v>
       </c>
@@ -1238,18 +1238,18 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
-      <c r="B13" s="21" t="s">
+      <c r="A13" s="20"/>
+      <c r="B13" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21" t="s">
+      <c r="C13" s="19"/>
+      <c r="D13" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="24">
         <v>11700</v>
       </c>
       <c r="G13" s="13" t="s">
@@ -1261,20 +1261,20 @@
       <c r="I13" s="8">
         <v>28</v>
       </c>
-      <c r="J13" s="21" t="s">
+      <c r="J13" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="K13" s="21" t="s">
+      <c r="K13" s="19" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="26"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="29"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="25"/>
       <c r="G14" s="13" t="s">
         <v>67</v>
       </c>
@@ -1284,16 +1284,16 @@
       <c r="I14" s="8">
         <v>12</v>
       </c>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="26"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="30"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="26"/>
       <c r="G15" s="14" t="s">
         <v>28</v>
       </c>
@@ -1303,22 +1303,22 @@
       <c r="I15" s="6">
         <v>59</v>
       </c>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="26"/>
-      <c r="B16" s="19" t="s">
+      <c r="A16" s="20"/>
+      <c r="B16" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19" t="s">
+      <c r="C16" s="22"/>
+      <c r="D16" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="27">
         <v>1400</v>
       </c>
       <c r="G16" s="15" t="s">
@@ -1330,20 +1330,20 @@
       <c r="I16" s="9">
         <v>49</v>
       </c>
-      <c r="J16" s="19" t="s">
+      <c r="J16" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="K16" s="19" t="s">
+      <c r="K16" s="22" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="26"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="31"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="28"/>
       <c r="G17" s="16" t="s">
         <v>28</v>
       </c>
@@ -1353,11 +1353,11 @@
       <c r="I17" s="7">
         <v>19</v>
       </c>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="26"/>
+      <c r="A18" s="20"/>
       <c r="B18" s="8" t="s">
         <v>10</v>
       </c>
@@ -1380,7 +1380,7 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="26"/>
+      <c r="A19" s="20"/>
       <c r="B19" s="9" t="s">
         <v>11</v>
       </c>
@@ -1405,8 +1405,8 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15.05" x14ac:dyDescent="0.25">
-      <c r="A20" s="26"/>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="20"/>
       <c r="B20" s="5" t="s">
         <v>12</v>
       </c>
@@ -1440,7 +1440,7 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="26"/>
+      <c r="A21" s="20"/>
       <c r="C21" s="2" t="s">
         <v>14</v>
       </c>
@@ -1453,7 +1453,7 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="26"/>
+      <c r="A22" s="20"/>
       <c r="C22" s="2" t="s">
         <v>15</v>
       </c>
@@ -1466,7 +1466,7 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="26"/>
+      <c r="A23" s="20"/>
       <c r="C23" s="2" t="s">
         <v>16</v>
       </c>
@@ -1479,7 +1479,7 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="26"/>
+      <c r="A24" s="20"/>
       <c r="C24" s="2" t="s">
         <v>17</v>
       </c>
@@ -1492,7 +1492,7 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="26"/>
+      <c r="A25" s="20"/>
       <c r="C25" s="2" t="s">
         <v>18</v>
       </c>
@@ -1505,7 +1505,7 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="22"/>
+      <c r="A26" s="21"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
         <v>25</v>
@@ -1524,7 +1524,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>21</v>
       </c>
@@ -1558,20 +1558,43 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="14.45" x14ac:dyDescent="0.25">
       <c r="G28" s="17"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="14.45" x14ac:dyDescent="0.25">
       <c r="G29" s="17"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="14.45" x14ac:dyDescent="0.25">
       <c r="G30" s="17"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="14.45" x14ac:dyDescent="0.25">
       <c r="G31" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="J2:J5"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="D6:D7"/>
     <mergeCell ref="A2:A26"/>
     <mergeCell ref="L2:L5"/>
     <mergeCell ref="L6:L7"/>
@@ -1588,29 +1611,6 @@
     <mergeCell ref="K2:K5"/>
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="B13:B15"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="J2:J5"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="K16:K17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/tables/Pop_Sizes.xlsx
+++ b/tables/Pop_Sizes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_RWD\Bison_github\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0ADDC20-9953-4F5E-AE86-D5035243767F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC36E7F-4DA5-4700-9434-78705603EC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,9 +82,6 @@
   </si>
   <si>
     <t>Peace Athabasca Delta</t>
-  </si>
-  <si>
-    <t>Subsepcies</t>
   </si>
   <si>
     <t>Wood Bison</t>
@@ -397,6 +394,9 @@
   </si>
   <si>
     <t xml:space="preserve">   </t>
+  </si>
+  <si>
+    <t>Subspecies</t>
   </si>
 </sst>
 </file>
@@ -565,40 +565,40 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -889,7 +889,7 @@
     <col min="3" max="4" width="23.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="10.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="22.28515625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="47.7109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="49.85546875" style="2" customWidth="1"/>
     <col min="8" max="8" width="16.5703125" style="2" customWidth="1"/>
     <col min="9" max="9" width="40.85546875" style="2" customWidth="1"/>
     <col min="10" max="10" width="26.28515625" style="2" customWidth="1"/>
@@ -901,7 +901,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17.100000000000001" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -910,52 +910,52 @@
         <v>13</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="29"/>
+      <c r="C2" s="24"/>
       <c r="D2" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E2" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="27">
         <v>11000</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H2" s="8">
         <v>1986</v>
@@ -963,25 +963,25 @@
       <c r="I2" s="8">
         <v>34</v>
       </c>
-      <c r="J2" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L2" s="20" t="s">
-        <v>65</v>
+      <c r="J2" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
       <c r="G3" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H3" s="6">
         <v>1989</v>
@@ -989,19 +989,19 @@
       <c r="I3" s="6">
         <v>10</v>
       </c>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="20"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
       <c r="G4" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H4" s="8">
         <v>1990</v>
@@ -1009,19 +1009,19 @@
       <c r="I4" s="8">
         <v>50</v>
       </c>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="20"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
+      <c r="A5" s="23"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
       <c r="G5" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H5" s="6">
         <v>1992</v>
@@ -1029,27 +1029,27 @@
       <c r="I5" s="6">
         <v>48</v>
       </c>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="20"/>
-      <c r="B6" s="22" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="22" t="s">
+      <c r="C6" s="21"/>
+      <c r="D6" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="28">
         <v>3800</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H6" s="9">
         <v>1991</v>
@@ -1057,23 +1057,23 @@
       <c r="I6" s="9">
         <v>13</v>
       </c>
-      <c r="J6" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="L6" s="22"/>
+      <c r="J6" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="21"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="20"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
       <c r="G7" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H7" s="7">
         <v>1993</v>
@@ -1081,27 +1081,27 @@
       <c r="I7" s="7">
         <v>9</v>
       </c>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="20"/>
+      <c r="A8" s="23"/>
       <c r="B8" s="19" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F8" s="19">
         <v>58</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H8" s="8">
         <v>1965</v>
@@ -1111,19 +1111,19 @@
       </c>
       <c r="J8" s="19"/>
       <c r="K8" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L8" s="19"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="20"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
       <c r="G9" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H9" s="6">
         <v>1968</v>
@@ -1131,27 +1131,27 @@
       <c r="I9" s="6">
         <v>2</v>
       </c>
-      <c r="J9" s="21"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="21"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="20"/>
+      <c r="A10" s="23"/>
       <c r="B10" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F10" s="11">
         <v>5000</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H10" s="9">
         <v>2000</v>
@@ -1160,32 +1160,32 @@
         <v>24</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="20"/>
+      <c r="A11" s="23"/>
       <c r="B11" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F11" s="12">
         <v>9000</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H11" s="8">
         <v>1984</v>
@@ -1194,32 +1194,32 @@
         <v>29</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="20"/>
+      <c r="A12" s="23"/>
       <c r="B12" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F12" s="11">
         <v>21000</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H12" s="9">
         <v>1963</v>
@@ -1228,32 +1228,32 @@
         <v>18</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="20"/>
+      <c r="A13" s="23"/>
       <c r="B13" s="19" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="19"/>
       <c r="D13" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="24">
+        <v>23</v>
+      </c>
+      <c r="F13" s="27">
         <v>11700</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H13" s="8">
         <v>1981</v>
@@ -1262,21 +1262,21 @@
         <v>28</v>
       </c>
       <c r="J13" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="25"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="29"/>
       <c r="G14" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H14" s="8">
         <v>1989</v>
@@ -1284,18 +1284,18 @@
       <c r="I14" s="8">
         <v>12</v>
       </c>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="20"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="26"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="30"/>
       <c r="G15" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H15" s="6">
         <v>1998</v>
@@ -1303,26 +1303,26 @@
       <c r="I15" s="6">
         <v>59</v>
       </c>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="20"/>
-      <c r="B16" s="22" t="s">
+      <c r="A16" s="23"/>
+      <c r="B16" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="27">
+      <c r="C16" s="21"/>
+      <c r="D16" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="28">
         <v>1400</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H16" s="9">
         <v>1995</v>
@@ -1330,22 +1330,22 @@
       <c r="I16" s="9">
         <v>49</v>
       </c>
-      <c r="J16" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="K16" s="22" t="s">
-        <v>53</v>
+      <c r="J16" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="K16" s="21" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="20"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="28"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="31"/>
       <c r="G17" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H17" s="7">
         <v>1999</v>
@@ -1353,165 +1353,165 @@
       <c r="I17" s="7">
         <v>19</v>
       </c>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="20"/>
+      <c r="A18" s="23"/>
       <c r="B18" s="8" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
       <c r="K18" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="20"/>
+      <c r="A19" s="23"/>
       <c r="B19" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
       <c r="K19" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="20"/>
+      <c r="A20" s="23"/>
       <c r="B20" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F20" s="10">
         <v>58000</v>
       </c>
       <c r="G20" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H20" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>61</v>
-      </c>
       <c r="J20" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="20"/>
+      <c r="A21" s="23"/>
       <c r="C21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G21" s="17"/>
       <c r="L21" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="20"/>
+      <c r="A22" s="23"/>
       <c r="C22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G22" s="17"/>
       <c r="L22" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="20"/>
+      <c r="A23" s="23"/>
       <c r="C23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G23" s="17"/>
       <c r="L23" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="20"/>
+      <c r="A24" s="23"/>
       <c r="C24" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G24" s="17"/>
       <c r="L24" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="20"/>
+      <c r="A25" s="23"/>
       <c r="C25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G25" s="17"/>
       <c r="L25" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="21"/>
+      <c r="A26" s="20"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
@@ -1521,41 +1521,41 @@
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
       <c r="L26" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>3</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F27" s="9">
         <v>136</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H27" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="I27" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="14.45" x14ac:dyDescent="0.25">
@@ -1572,29 +1572,6 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="J2:J5"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="D6:D7"/>
     <mergeCell ref="A2:A26"/>
     <mergeCell ref="L2:L5"/>
     <mergeCell ref="L6:L7"/>
@@ -1611,6 +1588,29 @@
     <mergeCell ref="K2:K5"/>
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="B13:B15"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="J2:J5"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="K16:K17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/tables/Pop_Sizes.xlsx
+++ b/tables/Pop_Sizes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_RWD\Bison_github\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC36E7F-4DA5-4700-9434-78705603EC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AA9A0A-CEC8-47CB-857A-D5FED518F8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="106">
   <si>
     <t>Population</t>
   </si>
@@ -397,6 +397,27 @@
   </si>
   <si>
     <t>Subspecies</t>
+  </si>
+  <si>
+    <t>Earliest Population Size Estimation (Year)</t>
+  </si>
+  <si>
+    <t>Population size as of COSEWIC Report (Year)</t>
+  </si>
+  <si>
+    <t>3,363 (2014)</t>
+  </si>
+  <si>
+    <t>250 (2011)</t>
+  </si>
+  <si>
+    <t>BC, NWT, &amp; YT</t>
+  </si>
+  <si>
+    <t>Elk Island National Park (Wood)</t>
+  </si>
+  <si>
+    <t>Elk Island National Park (Plains)</t>
   </si>
 </sst>
 </file>
@@ -508,7 +529,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -599,6 +620,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -881,18 +908,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.5703125" style="2" customWidth="1"/>
     <col min="2" max="2" width="28.5703125" style="2" customWidth="1"/>
     <col min="3" max="4" width="23.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" style="2" customWidth="1"/>
     <col min="7" max="7" width="49.85546875" style="2" customWidth="1"/>
     <col min="8" max="8" width="16.5703125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="40.85546875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="26.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="50.5703125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="49.5703125" style="2" customWidth="1"/>
     <col min="11" max="11" width="52.28515625" style="2" customWidth="1"/>
     <col min="12" max="12" width="27" style="2" customWidth="1"/>
     <col min="13" max="24" width="9.140625" style="2"/>
@@ -1337,7 +1364,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="23"/>
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
@@ -1356,7 +1383,7 @@
       <c r="J17" s="22"/>
       <c r="K17" s="22"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="23"/>
       <c r="B18" s="8" t="s">
         <v>10</v>
@@ -1379,7 +1406,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="23"/>
       <c r="B19" s="9" t="s">
         <v>11</v>
@@ -1405,7 +1432,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="23"/>
       <c r="B20" s="5" t="s">
         <v>12</v>
@@ -1439,7 +1466,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="23"/>
       <c r="C21" s="2" t="s">
         <v>14</v>
@@ -1452,7 +1479,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="23"/>
       <c r="C22" s="2" t="s">
         <v>15</v>
@@ -1465,7 +1492,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="23"/>
       <c r="C23" s="2" t="s">
         <v>16</v>
@@ -1478,7 +1505,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="23"/>
       <c r="C24" s="2" t="s">
         <v>17</v>
@@ -1491,7 +1518,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="23"/>
       <c r="C25" s="2" t="s">
         <v>18</v>
@@ -1504,7 +1531,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="20"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
@@ -1524,7 +1551,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="14.45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>20</v>
       </c>
@@ -1558,20 +1585,638 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="14.45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" ht="14.45" x14ac:dyDescent="0.25">
       <c r="G28" s="17"/>
     </row>
-    <row r="29" spans="1:12" ht="14.45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" ht="14.45" x14ac:dyDescent="0.25">
       <c r="G29" s="17"/>
     </row>
-    <row r="30" spans="1:12" ht="14.45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" ht="14.45" x14ac:dyDescent="0.25">
       <c r="G30" s="17"/>
     </row>
-    <row r="31" spans="1:12" ht="14.45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" ht="14.45" x14ac:dyDescent="0.25">
       <c r="G31" s="17"/>
     </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A33" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="24"/>
+      <c r="C33" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33" s="8">
+        <v>1986</v>
+      </c>
+      <c r="F33" s="8">
+        <v>34</v>
+      </c>
+      <c r="G33" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="H33" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="I33" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="W33" s="3"/>
+      <c r="X33" s="3"/>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A34" s="23"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E34" s="6">
+        <v>1989</v>
+      </c>
+      <c r="F34" s="6">
+        <v>10</v>
+      </c>
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A35" s="23"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E35" s="8">
+        <v>1990</v>
+      </c>
+      <c r="F35" s="8">
+        <v>50</v>
+      </c>
+      <c r="G35" s="23"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="23"/>
+      <c r="W35" s="3"/>
+      <c r="X35" s="3"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A36" s="20"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" s="6">
+        <v>1992</v>
+      </c>
+      <c r="F36" s="6">
+        <v>48</v>
+      </c>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="W36" s="3"/>
+      <c r="X36" s="3"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A37" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" s="9">
+        <v>1991</v>
+      </c>
+      <c r="F37" s="9">
+        <v>13</v>
+      </c>
+      <c r="G37" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="H37" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I37" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="W37" s="3"/>
+      <c r="X37" s="3"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A38" s="22"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38" s="7">
+        <v>1993</v>
+      </c>
+      <c r="F38" s="7">
+        <v>9</v>
+      </c>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="W38" s="3"/>
+      <c r="X38" s="3"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A39" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E39" s="8">
+        <v>1965</v>
+      </c>
+      <c r="F39" s="8">
+        <v>11</v>
+      </c>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="I39" s="19">
+        <v>300</v>
+      </c>
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A40" s="20"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="6">
+        <v>1968</v>
+      </c>
+      <c r="F40" s="6">
+        <v>2</v>
+      </c>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41" s="9">
+        <v>2000</v>
+      </c>
+      <c r="F41" s="9">
+        <v>24</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="W41" s="3"/>
+      <c r="X41" s="3"/>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A42" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" s="8">
+        <v>1984</v>
+      </c>
+      <c r="F42" s="8">
+        <v>29</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" s="9">
+        <v>1963</v>
+      </c>
+      <c r="F43" s="9">
+        <v>18</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="W43" s="3"/>
+      <c r="X43" s="3"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A44" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="19"/>
+      <c r="C44" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="8">
+        <v>1981</v>
+      </c>
+      <c r="F44" s="8">
+        <v>28</v>
+      </c>
+      <c r="G44" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="H44" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="I44" s="19"/>
+      <c r="W44" s="3"/>
+      <c r="X44" s="3"/>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A45" s="23"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E45" s="8">
+        <v>1989</v>
+      </c>
+      <c r="F45" s="8">
+        <v>12</v>
+      </c>
+      <c r="G45" s="23"/>
+      <c r="H45" s="23"/>
+      <c r="I45" s="33"/>
+      <c r="W45" s="3"/>
+      <c r="X45" s="3"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A46" s="20"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E46" s="6">
+        <v>1998</v>
+      </c>
+      <c r="F46" s="6">
+        <v>59</v>
+      </c>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="W46" s="3"/>
+      <c r="X46" s="3"/>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A47" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="21"/>
+      <c r="C47" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E47" s="9">
+        <v>1995</v>
+      </c>
+      <c r="F47" s="9">
+        <v>49</v>
+      </c>
+      <c r="G47" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H47" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="I47" s="32"/>
+      <c r="W47" s="3"/>
+      <c r="X47" s="3"/>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E48" s="7">
+        <v>1999</v>
+      </c>
+      <c r="F48" s="7">
+        <v>19</v>
+      </c>
+      <c r="G48" s="22"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="7"/>
+      <c r="W48" s="3"/>
+      <c r="X48" s="3"/>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A49" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I49" s="6"/>
+      <c r="W49" s="3"/>
+      <c r="X49" s="3"/>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A50" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G50" s="9"/>
+      <c r="H50" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="W50" s="3"/>
+      <c r="X50" s="3"/>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="W51" s="3"/>
+      <c r="X51" s="3"/>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="17"/>
+      <c r="I52" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="W52" s="3"/>
+      <c r="X52" s="3"/>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="17"/>
+      <c r="I53" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="W53" s="3"/>
+      <c r="X53" s="3"/>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B54" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D54" s="17"/>
+      <c r="I54" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="W54" s="3"/>
+      <c r="X54" s="3"/>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B55" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" s="17"/>
+      <c r="I55" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B56" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D56" s="17"/>
+      <c r="I56" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A57" s="6"/>
+      <c r="B57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="W57" s="3"/>
+      <c r="X57" s="3"/>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A58" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F58" s="9">
+        <v>48</v>
+      </c>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I58" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="W58" s="3"/>
+      <c r="X58" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="68">
+    <mergeCell ref="H44:H46"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="I44:I46"/>
+    <mergeCell ref="H33:H36"/>
+    <mergeCell ref="I33:I36"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="G33:G36"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="G44:G46"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C33:C36"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
     <mergeCell ref="A2:A26"/>
     <mergeCell ref="L2:L5"/>
     <mergeCell ref="L6:L7"/>
